--- a/outputs/ym/ym_unitka_fbo_fbs_2026-08-17.xlsx
+++ b/outputs/ym/ym_unitka_fbo_fbs_2026-08-17.xlsx
@@ -1242,7 +1242,7 @@
         <v/>
       </c>
       <c r="N16" s="47" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O16" s="29">
         <f>H16*N16</f>
@@ -1375,7 +1375,7 @@
         <v/>
       </c>
       <c r="N17" s="47" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O17" s="29">
         <f>H17*N17</f>
@@ -1509,7 +1509,7 @@
         <v/>
       </c>
       <c r="N18" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O18" s="29">
         <f>H18*N18</f>
@@ -1684,7 +1684,7 @@
         <v/>
       </c>
       <c r="N20" s="47" t="n">
-        <v>0.41</v>
+        <v>0.405</v>
       </c>
       <c r="O20" s="29">
         <f>H20*N20</f>
@@ -1861,7 +1861,7 @@
         <v/>
       </c>
       <c r="N22" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O22" s="29">
         <f>H22*N22</f>
@@ -2038,7 +2038,7 @@
         <v/>
       </c>
       <c r="N24" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O24" s="29">
         <f>H24*N24</f>
@@ -2215,7 +2215,7 @@
         <v/>
       </c>
       <c r="N26" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O26" s="29">
         <f>H26*N26</f>
@@ -2348,7 +2348,7 @@
         <v/>
       </c>
       <c r="N27" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O27" s="29">
         <f>H27*N27</f>
@@ -2482,7 +2482,7 @@
         <v/>
       </c>
       <c r="N28" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O28" s="29">
         <f>H28*N28</f>
@@ -2662,7 +2662,7 @@
         <v/>
       </c>
       <c r="N30" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O30" s="29">
         <f>H30*N30</f>
@@ -2797,7 +2797,7 @@
         <v/>
       </c>
       <c r="N31" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O31" s="29">
         <f>H31*N31</f>
@@ -2935,7 +2935,7 @@
         <v/>
       </c>
       <c r="N32" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O32" s="29">
         <f>H32*N32</f>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="N33" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O33" s="29">
         <f>H33*N33</f>
@@ -3207,7 +3207,7 @@
         <v/>
       </c>
       <c r="N34" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O34" s="29">
         <f>H34*N34</f>
@@ -3341,7 +3341,7 @@
         <v/>
       </c>
       <c r="N35" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O35" s="29">
         <f>H35*N35</f>
@@ -3475,7 +3475,7 @@
         <v/>
       </c>
       <c r="N36" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O36" s="29">
         <f>H36*N36</f>
@@ -3609,7 +3609,7 @@
         <v/>
       </c>
       <c r="N37" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O37" s="29">
         <f>H37*N37</f>
@@ -3743,7 +3743,7 @@
         <v/>
       </c>
       <c r="N38" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O38" s="29">
         <f>H38*N38</f>
@@ -3878,7 +3878,7 @@
         <v/>
       </c>
       <c r="N39" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O39" s="29">
         <f>H39*N39</f>
@@ -4406,7 +4406,7 @@
         <v/>
       </c>
       <c r="N43" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O43" s="29">
         <f>H43*N43</f>
@@ -5038,7 +5038,7 @@
         <v/>
       </c>
       <c r="N49" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O49" s="29">
         <f>H49*N49</f>
@@ -5180,7 +5180,7 @@
         <v/>
       </c>
       <c r="N50" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O50" s="29">
         <f>H50*N50</f>
@@ -5317,7 +5317,7 @@
         <v/>
       </c>
       <c r="N51" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O51" s="29">
         <f>H51*N51</f>
@@ -5459,7 +5459,7 @@
         <v/>
       </c>
       <c r="N52" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O52" s="29">
         <f>H52*N52</f>
@@ -5594,7 +5594,7 @@
         <v/>
       </c>
       <c r="N53" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O53" s="29">
         <f>H53*N53</f>
@@ -5733,7 +5733,7 @@
         <v/>
       </c>
       <c r="N54" s="34" t="n">
-        <v>0.41</v>
+        <v>0.405</v>
       </c>
       <c r="O54" s="29">
         <f>H54*N54</f>
@@ -5872,7 +5872,7 @@
         <v/>
       </c>
       <c r="N55" s="34" t="n">
-        <v>0.41</v>
+        <v>0.405</v>
       </c>
       <c r="O55" s="29">
         <f>H55*N55</f>
@@ -6141,7 +6141,7 @@
         <v/>
       </c>
       <c r="N57" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O57" s="29">
         <f>H57*N57</f>
@@ -6673,7 +6673,7 @@
         <v/>
       </c>
       <c r="N63" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O63" s="29">
         <f>H63*N63</f>
@@ -6807,7 +6807,7 @@
         <v/>
       </c>
       <c r="N64" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O64" s="29">
         <f>H64*N64</f>
@@ -6941,7 +6941,7 @@
         <v/>
       </c>
       <c r="N65" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O65" s="29">
         <f>H65*N65</f>
@@ -7116,7 +7116,7 @@
         <v/>
       </c>
       <c r="N67" s="47" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O67" s="29">
         <f>H67*N67</f>
@@ -7292,7 +7292,7 @@
         <v/>
       </c>
       <c r="N69" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O69" s="29">
         <f>H69*N69</f>
@@ -7426,7 +7426,7 @@
         <v/>
       </c>
       <c r="N70" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O70" s="29">
         <f>H70*N70</f>
@@ -7560,7 +7560,7 @@
         <v/>
       </c>
       <c r="N71" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O71" s="29">
         <f>H71*N71</f>
@@ -7694,7 +7694,7 @@
         <v/>
       </c>
       <c r="N72" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O72" s="29">
         <f>H72*N72</f>
@@ -8399,7 +8399,7 @@
         <v/>
       </c>
       <c r="N80" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O80" s="29">
         <f>H80*N80</f>
@@ -8579,7 +8579,7 @@
         <v/>
       </c>
       <c r="N82" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O82" s="29">
         <f>H82*N82</f>
@@ -8721,7 +8721,7 @@
         <v/>
       </c>
       <c r="N83" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O83" s="29">
         <f>H83*N83</f>
@@ -8863,7 +8863,7 @@
         <v/>
       </c>
       <c r="N84" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O84" s="29">
         <f>H84*N84</f>
@@ -9281,7 +9281,7 @@
         <v/>
       </c>
       <c r="N87" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O87" s="29">
         <f>H87*N87</f>
@@ -9456,7 +9456,7 @@
         <v/>
       </c>
       <c r="N89" s="47" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O89" s="29">
         <f>H89*N89</f>
@@ -12496,7 +12496,7 @@
         <v/>
       </c>
       <c r="N114" s="47" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O114" s="29">
         <f>H114*N114</f>
@@ -12758,7 +12758,7 @@
         <v/>
       </c>
       <c r="N116" s="47" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O116" s="29">
         <f>H116*N116</f>
@@ -12891,7 +12891,7 @@
         <v/>
       </c>
       <c r="N117" s="47" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O117" s="29">
         <f>H117*N117</f>
@@ -13029,7 +13029,7 @@
         <v/>
       </c>
       <c r="N118" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O118" s="29">
         <f>H118*N118</f>
@@ -13204,7 +13204,7 @@
         <v/>
       </c>
       <c r="N120" s="47" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O120" s="29">
         <f>H120*N120</f>
@@ -13645,7 +13645,7 @@
         <v/>
       </c>
       <c r="N124" s="47" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O124" s="29">
         <f>H124*N124</f>
@@ -13820,7 +13820,7 @@
         <v/>
       </c>
       <c r="N126" s="47" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O126" s="29">
         <f>H126*N126</f>
@@ -13953,7 +13953,7 @@
         <v/>
       </c>
       <c r="N127" s="47" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O127" s="29">
         <f>H127*N127</f>
@@ -14135,7 +14135,7 @@
         <v/>
       </c>
       <c r="N129" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O129" s="29">
         <f>H129*N129</f>
@@ -14273,7 +14273,7 @@
         <v/>
       </c>
       <c r="N130" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O130" s="29">
         <f>H130*N130</f>
@@ -14415,7 +14415,7 @@
         <v/>
       </c>
       <c r="N131" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O131" s="29">
         <f>H131*N131</f>
@@ -14551,7 +14551,7 @@
         <v/>
       </c>
       <c r="N132" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O132" s="29">
         <f>H132*N132</f>
@@ -14684,7 +14684,7 @@
         <v/>
       </c>
       <c r="N133" s="47" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O133" s="29">
         <f>H133*N133</f>
@@ -14817,7 +14817,7 @@
         <v/>
       </c>
       <c r="N134" s="47" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O134" s="29">
         <f>H134*N134</f>
@@ -14953,7 +14953,7 @@
         <v/>
       </c>
       <c r="N135" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O135" s="29">
         <f>H135*N135</f>
@@ -15086,7 +15086,7 @@
         <v/>
       </c>
       <c r="N136" s="47" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O136" s="29">
         <f>H136*N136</f>
@@ -15222,7 +15222,7 @@
         <v/>
       </c>
       <c r="N137" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O137" s="29">
         <f>H137*N137</f>
@@ -15355,7 +15355,7 @@
         <v/>
       </c>
       <c r="N138" s="47" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O138" s="29">
         <f>H138*N138</f>
@@ -15488,7 +15488,7 @@
         <v/>
       </c>
       <c r="N139" s="47" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O139" s="29">
         <f>H139*N139</f>
@@ -15668,7 +15668,7 @@
         <v/>
       </c>
       <c r="N141" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O141" s="29">
         <f>H141*N141</f>
@@ -15806,7 +15806,7 @@
         <v/>
       </c>
       <c r="N142" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O142" s="29">
         <f>H142*N142</f>
@@ -16162,7 +16162,7 @@
         <v/>
       </c>
       <c r="N146" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O146" s="29">
         <f>H146*N146</f>
@@ -16298,7 +16298,7 @@
         <v/>
       </c>
       <c r="N147" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O147" s="29">
         <f>H147*N147</f>
@@ -16434,7 +16434,7 @@
         <v/>
       </c>
       <c r="N148" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O148" s="29">
         <f>H148*N148</f>
@@ -16570,7 +16570,7 @@
         <v/>
       </c>
       <c r="N149" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O149" s="29">
         <f>H149*N149</f>
@@ -16706,7 +16706,7 @@
         <v/>
       </c>
       <c r="N150" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O150" s="29">
         <f>H150*N150</f>
@@ -16842,7 +16842,7 @@
         <v/>
       </c>
       <c r="N151" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O151" s="29">
         <f>H151*N151</f>
@@ -16978,7 +16978,7 @@
         <v/>
       </c>
       <c r="N152" s="34" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O152" s="29">
         <f>H152*N152</f>
@@ -18403,7 +18403,7 @@
         <v/>
       </c>
       <c r="P15" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q15" s="29">
         <f>J15*P15</f>
@@ -19065,7 +19065,7 @@
         <v/>
       </c>
       <c r="P21" s="47" t="n">
-        <v>0.47</v>
+        <v>0.475</v>
       </c>
       <c r="Q21" s="29">
         <f>J21*P21</f>
@@ -21575,7 +21575,7 @@
         <v/>
       </c>
       <c r="P41" s="47" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q41" s="29">
         <f>J41*P41</f>
@@ -21718,7 +21718,7 @@
         <v/>
       </c>
       <c r="P42" s="47" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q42" s="29">
         <f>J42*P42</f>
@@ -21861,7 +21861,7 @@
         <v/>
       </c>
       <c r="P43" s="47" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q43" s="29">
         <f>J43*P43</f>
@@ -22191,7 +22191,7 @@
         <v/>
       </c>
       <c r="P46" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q46" s="29">
         <f>J46*P46</f>
@@ -22336,7 +22336,7 @@
         <v/>
       </c>
       <c r="P47" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q47" s="29">
         <f>J47*P47</f>
@@ -22481,7 +22481,7 @@
         <v/>
       </c>
       <c r="P48" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q48" s="29">
         <f>J48*P48</f>
@@ -23409,7 +23409,7 @@
         <v/>
       </c>
       <c r="P55" s="34" t="n">
-        <v>0.47</v>
+        <v>0.475</v>
       </c>
       <c r="Q55" s="29">
         <f>J55*P55</f>
@@ -23554,7 +23554,7 @@
         <v/>
       </c>
       <c r="P56" s="34" t="n">
-        <v>0.47</v>
+        <v>0.475</v>
       </c>
       <c r="Q56" s="29">
         <f>J56*P56</f>
@@ -23699,7 +23699,7 @@
         <v/>
       </c>
       <c r="P57" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q57" s="29">
         <f>J57*P57</f>
@@ -23993,7 +23993,7 @@
         <v/>
       </c>
       <c r="P59" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q59" s="29">
         <f>J59*P59</f>
@@ -24184,7 +24184,7 @@
         <v/>
       </c>
       <c r="P61" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q61" s="29">
         <f>J61*P61</f>
@@ -25675,7 +25675,7 @@
         <v/>
       </c>
       <c r="P74" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q74" s="29">
         <f>J74*P74</f>
@@ -25864,7 +25864,7 @@
         <v/>
       </c>
       <c r="P76" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q76" s="29">
         <f>J76*P76</f>
@@ -26055,7 +26055,7 @@
         <v/>
       </c>
       <c r="P78" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q78" s="29">
         <f>J78*P78</f>
@@ -26870,7 +26870,7 @@
         <v/>
       </c>
       <c r="P85" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q85" s="29">
         <f>J85*P85</f>
@@ -27015,7 +27015,7 @@
         <v/>
       </c>
       <c r="P86" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q86" s="29">
         <f>J86*P86</f>
@@ -27536,7 +27536,7 @@
         <v/>
       </c>
       <c r="P91" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q91" s="29">
         <f>J91*P91</f>
@@ -27675,7 +27675,7 @@
         <v/>
       </c>
       <c r="P92" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q92" s="29">
         <f>J92*P92</f>
@@ -27814,7 +27814,7 @@
         <v/>
       </c>
       <c r="P93" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q93" s="29">
         <f>J93*P93</f>
@@ -27953,7 +27953,7 @@
         <v/>
       </c>
       <c r="P94" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q94" s="29">
         <f>J94*P94</f>
@@ -28092,7 +28092,7 @@
         <v/>
       </c>
       <c r="P95" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q95" s="29">
         <f>J95*P95</f>
@@ -28231,7 +28231,7 @@
         <v/>
       </c>
       <c r="P96" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q96" s="29">
         <f>J96*P96</f>
@@ -28370,7 +28370,7 @@
         <v/>
       </c>
       <c r="P97" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q97" s="29">
         <f>J97*P97</f>
@@ -28509,7 +28509,7 @@
         <v/>
       </c>
       <c r="P98" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q98" s="29">
         <f>J98*P98</f>
@@ -28654,7 +28654,7 @@
         <v/>
       </c>
       <c r="P99" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q99" s="29">
         <f>J99*P99</f>
@@ -28799,7 +28799,7 @@
         <v/>
       </c>
       <c r="P100" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q100" s="29">
         <f>J100*P100</f>
@@ -28944,7 +28944,7 @@
         <v/>
       </c>
       <c r="P101" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q101" s="29">
         <f>J101*P101</f>
@@ -29089,7 +29089,7 @@
         <v/>
       </c>
       <c r="P102" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q102" s="29">
         <f>J102*P102</f>
@@ -29228,7 +29228,7 @@
         <v/>
       </c>
       <c r="P103" s="47" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q103" s="29">
         <f>J103*P103</f>
@@ -29367,7 +29367,7 @@
         <v/>
       </c>
       <c r="P104" s="47" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q104" s="29">
         <f>J104*P104</f>
@@ -29558,7 +29558,7 @@
         <v/>
       </c>
       <c r="P106" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q106" s="29">
         <f>J106*P106</f>
@@ -29703,7 +29703,7 @@
         <v/>
       </c>
       <c r="P107" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q107" s="29">
         <f>J107*P107</f>
@@ -29848,7 +29848,7 @@
         <v/>
       </c>
       <c r="P108" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q108" s="29">
         <f>J108*P108</f>
@@ -29993,7 +29993,7 @@
         <v/>
       </c>
       <c r="P109" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q109" s="29">
         <f>J109*P109</f>
@@ -30138,7 +30138,7 @@
         <v/>
       </c>
       <c r="P110" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q110" s="29">
         <f>J110*P110</f>
@@ -30283,7 +30283,7 @@
         <v/>
       </c>
       <c r="P111" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q111" s="29">
         <f>J111*P111</f>
@@ -30470,7 +30470,7 @@
         <v/>
       </c>
       <c r="P113" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q113" s="29">
         <f>J113*P113</f>
@@ -30748,7 +30748,7 @@
         <v/>
       </c>
       <c r="P115" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q115" s="29">
         <f>J115*P115</f>
@@ -31507,7 +31507,7 @@
         <v/>
       </c>
       <c r="P121" s="47" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q121" s="29">
         <f>J121*P121</f>
@@ -31692,7 +31692,7 @@
         <v/>
       </c>
       <c r="P123" s="47" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q123" s="29">
         <f>J123*P123</f>
@@ -34337,7 +34337,7 @@
         <v/>
       </c>
       <c r="P145" s="34" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q145" s="29">
         <f>J145*P145</f>
